--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Preferences" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'History'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'History'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Preferences'!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,21 +430,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,12 +507,22 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Feedback Source</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Calendar Conflict</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Learned As</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:N1"/>
   <dataValidations count="1">
     <dataValidation sqref="K2:K2002" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Interested,Maybe,Not Interested,Attended"</formula1>
@@ -526,11 +538,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="1" max="1"/>
-    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,12 +615,22 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Feedback Source</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Calendar Conflict</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Learned As</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
